--- a/src/utils/sxsyzlzq/shijiesai/第3次_4强表格.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/第3次_4强表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19050" windowHeight="12080" activeTab="3"/>
+    <workbookView windowWidth="8505" windowHeight="2340" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="四强英雄出场率" sheetId="1" r:id="rId1"/>
@@ -1291,10 +1291,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="18.3636363636364" customWidth="1"/>
-    <col min="6" max="6" width="12.8181818181818"/>
+    <col min="1" max="1" width="18.3666666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.8166666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1331,11 +1331,11 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <f>SUM(C2,D2)</f>
+        <f t="shared" ref="E2:E29" si="0">SUM(C2,D2)</f>
         <v>1</v>
       </c>
       <c r="F2">
-        <f>C2/E2</f>
+        <f t="shared" ref="F2:F29" si="1">C2/E2</f>
         <v>1</v>
       </c>
     </row>
@@ -1353,11 +1353,11 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>SUM(C3,D3)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F3">
-        <f>C3/E3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <f>SUM(C4,D4)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="F4">
-        <f>C4/E4</f>
+        <f t="shared" si="1"/>
         <v>0.6875</v>
       </c>
     </row>
@@ -1397,11 +1397,11 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <f>SUM(C5,D5)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F5">
-        <f>C5/E5</f>
+        <f t="shared" si="1"/>
         <v>0.666666666666667</v>
       </c>
     </row>
@@ -1419,11 +1419,11 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <f>SUM(C6,D6)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F6">
-        <f>C6/E6</f>
+        <f t="shared" si="1"/>
         <v>0.666666666666667</v>
       </c>
     </row>
@@ -1441,11 +1441,11 @@
         <v>3</v>
       </c>
       <c r="E7">
-        <f>SUM(C7,D7)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F7">
-        <f>C7/E7</f>
+        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
     </row>
@@ -1463,11 +1463,11 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <f>SUM(C8,D8)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="F8">
-        <f>C8/E8</f>
+        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
     </row>
@@ -1485,11 +1485,11 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <f>SUM(C9,D9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="F9">
-        <f>C9/E9</f>
+        <f t="shared" si="1"/>
         <v>0.619047619047619</v>
       </c>
     </row>
@@ -1507,11 +1507,11 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <f>SUM(C10,D10)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F10">
-        <f>C10/E10</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
     </row>
@@ -1529,11 +1529,11 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <f>SUM(C11,D11)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="F11">
-        <f>C11/E11</f>
+        <f t="shared" si="1"/>
         <v>0.575</v>
       </c>
     </row>
@@ -1551,11 +1551,11 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <f>SUM(C12,D12)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F12">
-        <f>C12/E12</f>
+        <f t="shared" si="1"/>
         <v>0.555555555555556</v>
       </c>
     </row>
@@ -1573,11 +1573,11 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <f>SUM(C13,D13)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F13">
-        <f>C13/E13</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1595,11 +1595,11 @@
         <v>7</v>
       </c>
       <c r="E14">
-        <f>SUM(C14,D14)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="F14">
-        <f>C14/E14</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1617,11 +1617,11 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <f>SUM(C15,D15)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F15">
-        <f>C15/E15</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1639,11 +1639,11 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <f>SUM(C16,D16)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F16">
-        <f>C16/E16</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1661,11 +1661,11 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <f>SUM(C17,D17)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F17">
-        <f>C17/E17</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1683,11 +1683,11 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <f>SUM(C18,D18)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F18">
-        <f>C18/E18</f>
+        <f t="shared" si="1"/>
         <v>0.444444444444444</v>
       </c>
     </row>
@@ -1705,11 +1705,11 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <f>SUM(C19,D19)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="F19">
-        <f>C19/E19</f>
+        <f t="shared" si="1"/>
         <v>0.421052631578947</v>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <f>SUM(C20,D20)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="F20">
-        <f>C20/E20</f>
+        <f t="shared" si="1"/>
         <v>0.421052631578947</v>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         <v>6</v>
       </c>
       <c r="E21">
-        <f>SUM(C21,D21)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F21">
-        <f>C21/E21</f>
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
@@ -1771,11 +1771,11 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <f>SUM(C22,D22)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F22">
-        <f>C22/E22</f>
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
@@ -1793,11 +1793,11 @@
         <v>17</v>
       </c>
       <c r="E23">
-        <f>SUM(C23,D23)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="F23">
-        <f>C23/E23</f>
+        <f t="shared" si="1"/>
         <v>0.392857142857143</v>
       </c>
     </row>
@@ -1815,11 +1815,11 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <f>SUM(C24,D24)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F24">
-        <f>C24/E24</f>
+        <f t="shared" si="1"/>
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -1837,11 +1837,11 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <f>SUM(C25,D25)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F25">
-        <f>C25/E25</f>
+        <f t="shared" si="1"/>
         <v>0.272727272727273</v>
       </c>
     </row>
@@ -1859,11 +1859,11 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <f>SUM(C26,D26)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F26">
-        <f>C26/E26</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
@@ -1881,11 +1881,11 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <f>SUM(C27,D27)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F27">
-        <f>C27/E27</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1903,11 +1903,11 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <f>SUM(C28,D28)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F28">
-        <f>C28/E28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1925,11 +1925,11 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <f>SUM(C29,D29)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F29">
-        <f>C29/E29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="13.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="13.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="12.9083333333333" customWidth="1"/>
+    <col min="4" max="4" width="13.6333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.275" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2170,10 +2170,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9.63636363636364" customWidth="1"/>
-    <col min="5" max="5" width="12.8181818181818"/>
+    <col min="1" max="1" width="9.63333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.8166666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2204,11 +2204,11 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>SUM(B2,C2)</f>
+        <f t="shared" ref="D2:D29" si="0">SUM(B2,C2)</f>
         <v>4</v>
       </c>
       <c r="E2">
-        <f>B2/D2</f>
+        <f t="shared" ref="E2:E29" si="1">B2/D2</f>
         <v>1</v>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <f>SUM(B3,C3)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E3">
-        <f>B3/D3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2242,11 +2242,11 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <f>SUM(B4,C4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E4">
-        <f>B4/D4</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2261,11 +2261,11 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <f>SUM(B5,C5)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="E5">
-        <f>B5/D5</f>
+        <f t="shared" si="1"/>
         <v>0.777777777777778</v>
       </c>
     </row>
@@ -2280,11 +2280,11 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <f>SUM(B6,C6)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E6">
-        <f>B6/D6</f>
+        <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
@@ -2299,11 +2299,11 @@
         <v>11</v>
       </c>
       <c r="D7">
-        <f>SUM(B7,C7)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="E7">
-        <f>B7/D7</f>
+        <f t="shared" si="1"/>
         <v>0.717948717948718</v>
       </c>
     </row>
@@ -2318,11 +2318,11 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <f>SUM(B8,C8)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="E8">
-        <f>B8/D8</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
     </row>
@@ -2337,11 +2337,11 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <f>SUM(B9,C9)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="E9">
-        <f>B9/D9</f>
+        <f t="shared" si="1"/>
         <v>0.5625</v>
       </c>
     </row>
@@ -2356,11 +2356,11 @@
         <v>4</v>
       </c>
       <c r="D10">
-        <f>SUM(B10,C10)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="E10">
-        <f>B10/D10</f>
+        <f t="shared" si="1"/>
         <v>0.555555555555556</v>
       </c>
     </row>
@@ -2375,11 +2375,11 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <f>SUM(B11,C11)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E11">
-        <f>B11/D11</f>
+        <f t="shared" si="1"/>
         <v>0.545454545454545</v>
       </c>
     </row>
@@ -2394,11 +2394,11 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <f>SUM(B12,C12)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E12">
-        <f>B12/D12</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -2413,11 +2413,11 @@
         <v>13</v>
       </c>
       <c r="D13">
-        <f>SUM(B13,C13)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="E13">
-        <f>B13/D13</f>
+        <f t="shared" si="1"/>
         <v>0.48</v>
       </c>
     </row>
@@ -2432,11 +2432,11 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <f>SUM(B14,C14)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="E14">
-        <f>B14/D14</f>
+        <f t="shared" si="1"/>
         <v>0.473684210526316</v>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         <v>11</v>
       </c>
       <c r="D15">
-        <f>SUM(B15,C15)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="E15">
-        <f>B15/D15</f>
+        <f t="shared" si="1"/>
         <v>0.388888888888889</v>
       </c>
     </row>
@@ -2470,11 +2470,11 @@
         <v>14</v>
       </c>
       <c r="D16">
-        <f>SUM(B16,C16)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="E16">
-        <f>B16/D16</f>
+        <f t="shared" si="1"/>
         <v>0.363636363636364</v>
       </c>
     </row>
@@ -2489,11 +2489,11 @@
         <v>9</v>
       </c>
       <c r="D17">
-        <f>SUM(B17,C17)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="E17">
-        <f>B17/D17</f>
+        <f t="shared" si="1"/>
         <v>0.357142857142857</v>
       </c>
     </row>
@@ -2508,11 +2508,11 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <f>SUM(B18,C18)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E18">
-        <f>B18/D18</f>
+        <f t="shared" si="1"/>
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -2527,11 +2527,11 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <f>SUM(B19,C19)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E19">
-        <f>B19/D19</f>
+        <f t="shared" si="1"/>
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -2546,11 +2546,11 @@
         <v>4</v>
       </c>
       <c r="D20">
-        <f>SUM(B20,C20)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E20">
-        <f>B20/D20</f>
+        <f t="shared" si="1"/>
         <v>0.333333333333333</v>
       </c>
     </row>
@@ -2565,11 +2565,11 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <f>SUM(B21,C21)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E21">
-        <f>B21/D21</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
@@ -2584,11 +2584,11 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <f>SUM(B22,C22)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="E22">
-        <f>B22/D22</f>
+        <f t="shared" si="1"/>
         <v>0.222222222222222</v>
       </c>
     </row>
@@ -2603,11 +2603,11 @@
         <v>4</v>
       </c>
       <c r="D23">
-        <f>SUM(B23,C23)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="E23">
-        <f>B23/D23</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
     </row>
@@ -2622,11 +2622,11 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <f>SUM(B24,C24)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E24">
-        <f>B24/D24</f>
+        <f t="shared" si="1"/>
         <v>0.166666666666667</v>
       </c>
     </row>
@@ -2641,11 +2641,11 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <f>SUM(B25,C25)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E25">
-        <f>B25/D25</f>
+        <f t="shared" si="1"/>
         <v>0.166666666666667</v>
       </c>
     </row>
@@ -2660,11 +2660,11 @@
         <v>2</v>
       </c>
       <c r="D26">
-        <f>SUM(B26,C26)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E26">
-        <f>B26/D26</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2679,11 +2679,11 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <f>SUM(B27,C27)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E27">
-        <f>B27/D27</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2698,11 +2698,11 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <f>SUM(B28,C28)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E28">
-        <f>B28/D28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2717,11 +2717,11 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <f>SUM(B29,C29)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E29">
-        <f>B29/D29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -2739,11 +2739,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.6363636363636" customWidth="1"/>
-    <col min="2" max="2" width="9.81818181818182" customWidth="1"/>
-    <col min="6" max="6" width="12.8181818181818"/>
+    <col min="1" max="1" width="19.6333333333333" customWidth="1"/>
+    <col min="2" max="2" width="9.81666666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.8166666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3032,20 +3032,20 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <f>SUM(C14,D14)</f>
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="F14">
         <f>C14/E14</f>
@@ -3076,20 +3076,20 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <f>SUM(C16,D16)</f>
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F16">
         <f>C16/E16</f>
@@ -3340,20 +3340,20 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <f>SUM(C28,D28)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <f>C28/E28</f>
@@ -3362,20 +3362,20 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <f>SUM(C29,D29)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <f>C29/E29</f>

--- a/src/utils/sxsyzlzq/shijiesai/第3次_4强表格.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/第3次_4强表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8505" windowHeight="2340" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="四强英雄出场率" sheetId="1" r:id="rId1"/>
@@ -366,11 +366,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -975,8 +976,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1334,8 +1338,8 @@
         <f t="shared" ref="E2:E29" si="0">SUM(C2,D2)</f>
         <v>1</v>
       </c>
-      <c r="F2">
-        <f t="shared" ref="F2:F29" si="1">C2/E2</f>
+      <c r="F2" s="1">
+        <f>C2/E2</f>
         <v>1</v>
       </c>
     </row>
@@ -1356,8 +1360,8 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F3">
-        <f t="shared" si="1"/>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F29" si="1">C3/E3</f>
         <v>1</v>
       </c>
     </row>
@@ -1378,7 +1382,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <f t="shared" si="1"/>
         <v>0.6875</v>
       </c>
@@ -1400,7 +1404,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <f t="shared" si="1"/>
         <v>0.666666666666667</v>
       </c>
@@ -1422,7 +1426,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <f t="shared" si="1"/>
         <v>0.666666666666667</v>
       </c>
@@ -1444,7 +1448,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
@@ -1466,7 +1470,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
@@ -1488,7 +1492,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <f t="shared" si="1"/>
         <v>0.619047619047619</v>
       </c>
@@ -1510,7 +1514,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -1532,7 +1536,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <f t="shared" si="1"/>
         <v>0.575</v>
       </c>
@@ -1554,7 +1558,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <f t="shared" si="1"/>
         <v>0.555555555555556</v>
       </c>
@@ -1576,7 +1580,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1598,7 +1602,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1620,7 +1624,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1642,7 +1646,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1664,7 +1668,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -1686,7 +1690,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <f t="shared" si="1"/>
         <v>0.444444444444444</v>
       </c>
@@ -1708,7 +1712,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <f t="shared" si="1"/>
         <v>0.421052631578947</v>
       </c>
@@ -1730,7 +1734,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f t="shared" si="1"/>
         <v>0.421052631578947</v>
       </c>
@@ -1752,7 +1756,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
@@ -1774,7 +1778,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
@@ -1796,7 +1800,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <f t="shared" si="1"/>
         <v>0.392857142857143</v>
       </c>
@@ -1818,7 +1822,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <f t="shared" si="1"/>
         <v>0.333333333333333</v>
       </c>
@@ -1840,7 +1844,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <f t="shared" si="1"/>
         <v>0.272727272727273</v>
       </c>
@@ -1862,7 +1866,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
@@ -1884,7 +1888,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1906,7 +1910,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1928,7 +1932,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2780,11 +2784,11 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <f>SUM(C2,D2)</f>
+        <f t="shared" ref="E2:E29" si="0">SUM(C2,D2)</f>
         <v>2</v>
       </c>
       <c r="F2">
-        <f>C2/E2</f>
+        <f t="shared" ref="F2:F29" si="1">C2/E2</f>
         <v>1</v>
       </c>
     </row>
@@ -2802,11 +2806,11 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>SUM(C3,D3)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F3">
-        <f>C3/E3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2824,11 +2828,11 @@
         <v>2</v>
       </c>
       <c r="E4">
-        <f>SUM(C4,D4)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F4">
-        <f>C4/E4</f>
+        <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
@@ -2846,11 +2850,11 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <f>SUM(C5,D5)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="F5">
-        <f>C5/E5</f>
+        <f t="shared" si="1"/>
         <v>0.647058823529412</v>
       </c>
     </row>
@@ -2868,11 +2872,11 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <f>SUM(C6,D6)</f>
+        <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="F6">
-        <f>C6/E6</f>
+        <f t="shared" si="1"/>
         <v>0.645569620253165</v>
       </c>
     </row>
@@ -2890,11 +2894,11 @@
         <v>15</v>
       </c>
       <c r="E7">
-        <f>SUM(C7,D7)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="F7">
-        <f>C7/E7</f>
+        <f t="shared" si="1"/>
         <v>0.594594594594595</v>
       </c>
     </row>
@@ -2912,11 +2916,11 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <f>SUM(C8,D8)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F8">
-        <f>C8/E8</f>
+        <f t="shared" si="1"/>
         <v>0.555555555555556</v>
       </c>
     </row>
@@ -2934,11 +2938,11 @@
         <v>22</v>
       </c>
       <c r="E9">
-        <f>SUM(C9,D9)</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="F9">
-        <f>C9/E9</f>
+        <f t="shared" si="1"/>
         <v>0.551020408163265</v>
       </c>
     </row>
@@ -2956,11 +2960,11 @@
         <v>18</v>
       </c>
       <c r="E10">
-        <f>SUM(C10,D10)</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="F10">
-        <f>C10/E10</f>
+        <f t="shared" si="1"/>
         <v>0.55</v>
       </c>
     </row>
@@ -2978,11 +2982,11 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <f>SUM(C11,D11)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="F11">
-        <f>C11/E11</f>
+        <f t="shared" si="1"/>
         <v>0.533333333333333</v>
       </c>
     </row>
@@ -3000,11 +3004,11 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <f>SUM(C12,D12)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="F12">
-        <f>C12/E12</f>
+        <f t="shared" si="1"/>
         <v>0.529411764705882</v>
       </c>
     </row>
@@ -3022,11 +3026,11 @@
         <v>11</v>
       </c>
       <c r="E13">
-        <f>SUM(C13,D13)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="F13">
-        <f>C13/E13</f>
+        <f t="shared" si="1"/>
         <v>0.521739130434783</v>
       </c>
     </row>
@@ -3044,11 +3048,11 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <f>SUM(C14,D14)</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="F14">
-        <f>C14/E14</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -3066,11 +3070,11 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <f>SUM(C15,D15)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F15">
-        <f>C15/E15</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -3088,11 +3092,11 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <f>SUM(C16,D16)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F16">
-        <f>C16/E16</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -3110,11 +3114,11 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <f>SUM(C17,D17)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F17">
-        <f>C17/E17</f>
+        <f t="shared" si="1"/>
         <v>0.416666666666667</v>
       </c>
     </row>
@@ -3132,11 +3136,11 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <f>SUM(C18,D18)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="F18">
-        <f>C18/E18</f>
+        <f t="shared" si="1"/>
         <v>0.390243902439024</v>
       </c>
     </row>
@@ -3154,11 +3158,11 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <f>SUM(C19,D19)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F19">
-        <f>C19/E19</f>
+        <f t="shared" si="1"/>
         <v>0.363636363636364</v>
       </c>
     </row>
@@ -3176,11 +3180,11 @@
         <v>13</v>
       </c>
       <c r="E20">
-        <f>SUM(C20,D20)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="F20">
-        <f>C20/E20</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
     </row>
@@ -3198,11 +3202,11 @@
         <v>17</v>
       </c>
       <c r="E21">
-        <f>SUM(C21,D21)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="F21">
-        <f>C21/E21</f>
+        <f t="shared" si="1"/>
         <v>0.32</v>
       </c>
     </row>
@@ -3220,11 +3224,11 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <f>SUM(C22,D22)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F22">
-        <f>C22/E22</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
@@ -3242,11 +3246,11 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <f>SUM(C23,D23)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F23">
-        <f>C23/E23</f>
+        <f t="shared" si="1"/>
         <v>0.285714285714286</v>
       </c>
     </row>
@@ -3264,11 +3268,11 @@
         <v>13</v>
       </c>
       <c r="E24">
-        <f>SUM(C24,D24)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F24">
-        <f>C24/E24</f>
+        <f t="shared" si="1"/>
         <v>0.277777777777778</v>
       </c>
     </row>
@@ -3286,11 +3290,11 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <f>SUM(C25,D25)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F25">
-        <f>C25/E25</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
@@ -3308,11 +3312,11 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <f>SUM(C26,D26)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F26">
-        <f>C26/E26</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
@@ -3330,11 +3334,11 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <f>SUM(C27,D27)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F27">
-        <f>C27/E27</f>
+        <f t="shared" si="1"/>
         <v>0.166666666666667</v>
       </c>
     </row>
@@ -3352,11 +3356,11 @@
         <v>3</v>
       </c>
       <c r="E28">
-        <f>SUM(C28,D28)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="F28">
-        <f>C28/E28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3374,11 +3378,11 @@
         <v>2</v>
       </c>
       <c r="E29">
-        <f>SUM(C29,D29)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="F29">
-        <f>C29/E29</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
